--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/auth-controller/login-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/auth-controller/login-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="91">
-  <si>
-    <t>Statement: auth-controller.login(data) – Server Action. Validates LoginUserInput (email regex + non-empty password). On valid input delegates to authService.login(), writes session fields, calls session.save(), and returns { success: true, data: SessionData }. On validation failure returns { success: false, errors }. On AppError returns { success: false, message }. On unexpected error returns { success: false, message: "An unexpected error occurred" }.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="104">
+  <si>
+    <t>Statement: login(data) – Validates the login input, authenticates the credentials, persists the resulting SessionData in the session cookie, and returns an ActionResult&lt;SessionData&gt;. Returns success with the SessionData on success with the session persisted. Returns a field-level validation error for schema failures without calling the authentication service. Returns a failure with the service error message for AuthorizationError and NotFoundError. Returns a failure with a generic error message for unexpected errors such as a session retrieval failure.</t>
   </si>
   <si>
     <t/>
@@ -31,27 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: LoginUserInput { email: string, password: string }</t>
+    <t>Input: data: LoginUserInput { email: string, password: string }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>authService.login and getSession are mock-injected; session.save is a jest.fn()</t>
+    <t>The session layer is available and supports save() and destroy(). Password rules: 8–64 chars, at least one uppercase letter, one digit, one special character.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;SessionData&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;SessionData&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t xml:space="preserve">On success: session is populated and saved.
-On validation failure: no service call, no session write.
-On error: session not written.</t>
+    <t>On success: login completes, session persisted, returned data matches the authenticated user session. On validation failure: field-level validation error returned, the authentication service is not called. On service error: operation fails with the thrown error message. On unexpected error: operation fails with generic error message.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -66,37 +64,58 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>email format</t>
-  </si>
-  <si>
-    <t>valid email address</t>
-  </si>
-  <si>
-    <t>invalid email format → validation error</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>non-empty password</t>
-  </si>
-  <si>
-    <t>empty password → validation error</t>
-  </si>
-  <si>
-    <t>service outcome</t>
-  </si>
-  <si>
-    <t>authService.login resolves</t>
-  </si>
-  <si>
-    <t>service throws AuthorizationError → failure with message</t>
-  </si>
-  <si>
-    <t>service throws NotFoundError → failure with message</t>
-  </si>
-  <si>
-    <t>service throws unexpected Error → generic failure</t>
+    <t>Credentials</t>
+  </si>
+  <si>
+    <t>Valid admin credentials → login succeeds, returned session data matches admin session, session persisted</t>
+  </si>
+  <si>
+    <t>Valid member credentials → login succeeds, returned session data matches member session with role MEMBER, session persisted</t>
+  </si>
+  <si>
+    <t>Email field</t>
+  </si>
+  <si>
+    <t>Missing email → validation fails: email field error returned</t>
+  </si>
+  <si>
+    <t>Password field</t>
+  </si>
+  <si>
+    <t>Missing password → validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>Email format</t>
+  </si>
+  <si>
+    <t>Invalid email format ("bad-email") → validation fails: email field error returned</t>
+  </si>
+  <si>
+    <t>Password rules</t>
+  </si>
+  <si>
+    <t>No uppercase letter ("validpass1!") → validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>No digit ("ValidPass!") → validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>No special character ("ValidPass1") → validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>Service error</t>
+  </si>
+  <si>
+    <t>Credentials do not match any account (AuthorizationError "Invalid email or password") → operation fails with message "Invalid email or password"</t>
+  </si>
+  <si>
+    <t>No account exists for the provided email (NotFoundError "User not found") → operation fails with message "User not found"</t>
+  </si>
+  <si>
+    <t>Session error</t>
+  </si>
+  <si>
+    <t>Session retrieval fails unexpectedly → operation fails with generic error message</t>
   </si>
   <si>
     <t>No TC</t>
@@ -114,55 +133,94 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1,3,5</t>
-  </si>
-  <si>
-    <t>email="admin@gymtrackerpro.com", password="ValidPass1!"</t>
-  </si>
-  <si>
-    <t>{ success: true }, session.save called</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>email="not-an-email", password="ValidPass1!"</t>
-  </si>
-  <si>
-    <t>{ success: false, errors defined }</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>email="admin@gymtrackerpro.com", password=""</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>valid input, service throws AuthorizationError("Invalid…")</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Invalid email or password" }</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>valid input, service throws NotFoundError("User not found")</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "User not found" }</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>valid input, service throws Error("DB down")</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "An unexpected error occurred" }</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>valid admin credentials (email and password matching an admin account)</t>
+  </si>
+  <si>
+    <t>login succeeds, returned session data matches admin session, session persisted</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>valid member credentials (email: "member@example.com", password: "ValidPassword1!")</t>
+  </si>
+  <si>
+    <t>login succeeds, returned session data matches member session with role MEMBER, session persisted</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>login data with email field omitted</t>
+  </si>
+  <si>
+    <t>validation fails: email field error returned</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>login data with password field omitted</t>
+  </si>
+  <si>
+    <t>validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>login data with email set to "bad-email"</t>
+  </si>
+  <si>
+    <t>EC-6</t>
+  </si>
+  <si>
+    <t>login data with password "validpass1!" (no uppercase letter)</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>login data with password "ValidPass!" (no digit)</t>
+  </si>
+  <si>
+    <t>EC-8</t>
+  </si>
+  <si>
+    <t>login data with password "ValidPass1" (no special character)</t>
+  </si>
+  <si>
+    <t>EC-9</t>
+  </si>
+  <si>
+    <t>valid credentials format, credentials do not match any account (AuthorizationError)</t>
+  </si>
+  <si>
+    <t>operation fails with message "Invalid email or password"</t>
+  </si>
+  <si>
+    <t>EC-10</t>
+  </si>
+  <si>
+    <t>valid credentials format, no account exists for the provided email (NotFoundError)</t>
+  </si>
+  <si>
+    <t>operation fails with message "User not found"</t>
+  </si>
+  <si>
+    <t>EC-11</t>
+  </si>
+  <si>
+    <t>valid credentials format, authentication succeeds, session retrieval fails unexpectedly</t>
+  </si>
+  <si>
+    <t>operation fails with generic error message</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -171,22 +229,55 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>password length boundary</t>
-  </si>
-  <si>
-    <t>password with 2 chars → valid (min+1)</t>
+    <t>Password length</t>
+  </si>
+  <si>
+    <t>7 chars (min - 1): below minimum → invalid; 8 chars (min): at minimum → valid; 9 chars (min + 1): above minimum → valid</t>
+  </si>
+  <si>
+    <t>63 chars (max - 1): below maximum → valid; 64 chars (max): at maximum → valid; 65 chars (max + 1): above maximum → invalid</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>password=2 chars</t>
-  </si>
-  <si>
-    <t>password="xy"</t>
-  </si>
-  <si>
-    <t>success=true (boundary valid)</t>
+    <t>BVA-1 (n=7)</t>
+  </si>
+  <si>
+    <t>login data with password of 7 characters meeting all rules except minimum length ("V1@aaaa")</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=8)</t>
+  </si>
+  <si>
+    <t>login data with password of 8 characters meeting all rules ("V1@aaaaa")</t>
+  </si>
+  <si>
+    <t>login succeeds, session persisted</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=9)</t>
+  </si>
+  <si>
+    <t>login data with password of 9 characters meeting all rules ("V1@aaaaaa")</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=63)</t>
+  </si>
+  <si>
+    <t>login data with password of 63 characters meeting all rules ("V1@" + "a".repeat(60))</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=64)</t>
+  </si>
+  <si>
+    <t>login data with password of 64 characters meeting all rules ("V1@" + "a".repeat(61))</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=65)</t>
+  </si>
+  <si>
+    <t>login data with password of 65 characters exceeding maximum length ("V1@" + "a".repeat(62))</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -195,61 +286,10 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>Valid credentials</t>
-  </si>
-  <si>
-    <t>success=true, session saved</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>Invalid email format</t>
-  </si>
-  <si>
-    <t>success=false, errors defined</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>Empty password</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>Service throws AuthorizationError</t>
-  </si>
-  <si>
-    <t>success=false, message from error</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
-    <t>Service throws NotFoundError</t>
-  </si>
-  <si>
-    <t>EP-6</t>
-  </si>
-  <si>
-    <t>Service throws unexpected Error</t>
-  </si>
-  <si>
-    <t>success=false, message="An unexpected error occurred"</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>Password 2 chars</t>
-  </si>
-  <si>
-    <t>success=true</t>
+    <t>BVA-2</t>
   </si>
   <si>
     <t>Testing</t>
@@ -282,16 +322,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>AUTH-01</t>
+    <t>CTRL-01</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -807,7 +844,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -848,13 +885,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -865,10 +902,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -876,13 +913,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -890,13 +927,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -904,13 +941,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -918,13 +955,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -932,13 +969,55 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -948,6 +1027,277 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="80" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -961,19 +1311,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -981,16 +1331,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -998,16 +1348,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1015,16 +1365,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1032,13 +1382,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>41</v>
@@ -1049,16 +1399,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1066,106 +1416,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="80" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1176,7 +1436,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1189,22 +1449,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1212,19 +1472,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1232,19 +1492,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1252,19 +1512,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1272,19 +1532,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1292,19 +1552,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1312,19 +1572,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1332,19 +1592,219 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>76</v>
+      <c r="E13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1372,16 +1832,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1389,45 +1849,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>87</v>
+      <c r="A3" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="B3" s="1">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1436,19 +1896,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>90</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
